--- a/ExcelFiles/New (2).xlsx
+++ b/ExcelFiles/New (2).xlsx
@@ -8,21 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\Excel_Github\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8237A774-9BBA-4351-9734-E46E39FAB90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E6AFDC-4A9A-47BE-B12C-552E63279169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4635" yWindow="2190" windowWidth="23400" windowHeight="11385" xr2:uid="{858A62D9-1599-4210-9775-AAAC6E0CE55F}"/>
+    <workbookView xWindow="5835" yWindow="2685" windowWidth="22500" windowHeight="11385" activeTab="2" xr2:uid="{858A62D9-1599-4210-9775-AAAC6E0CE55F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Practice" sheetId="2" r:id="rId1"/>
-    <sheet name="Solution" sheetId="3" r:id="rId2"/>
+    <sheet name="Frequency" sheetId="2" r:id="rId1"/>
+    <sheet name="Index &amp; Match" sheetId="4" r:id="rId2"/>
+    <sheet name="Lookup" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Commision_Rate" localSheetId="1">Solution!$G$10</definedName>
-    <definedName name="Sales_Officer">Practice!$A$3:$A$14</definedName>
-    <definedName name="Sales_Revenue">Practice!$C$3:$C$14</definedName>
-    <definedName name="Tax_Payable">Practice!$E$3:$E$14</definedName>
-    <definedName name="Tax_Rate" localSheetId="1">Solution!$G$13</definedName>
-    <definedName name="Total_Commision">Practice!$D$3:$D$14</definedName>
+    <definedName name="Commision_Rate" localSheetId="2">Lookup!$G$11</definedName>
+    <definedName name="Sales_Officer" localSheetId="1">'Index &amp; Match'!$A$3:$A$14</definedName>
+    <definedName name="Sales_Officer">Frequency!$A$3:$A$14</definedName>
+    <definedName name="Sales_Revenue" localSheetId="1">'Index &amp; Match'!$C$3:$C$14</definedName>
+    <definedName name="Sales_Revenue">Frequency!$C$3:$C$14</definedName>
+    <definedName name="Tax_Payable" localSheetId="1">'Index &amp; Match'!$E$3:$E$14</definedName>
+    <definedName name="Tax_Payable">Frequency!$E$3:$E$14</definedName>
+    <definedName name="Tax_Rate" localSheetId="2">Lookup!$G$14</definedName>
+    <definedName name="Total_Commision" localSheetId="1">'Index &amp; Match'!$D$3:$D$14</definedName>
+    <definedName name="Total_Commision">Frequency!$D$3:$D$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,13 +52,105 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="23">
+  <si>
+    <t>Emp ID</t>
+  </si>
+  <si>
+    <t>Emp Name</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Ashok Singh</t>
+  </si>
+  <si>
+    <t>Shankar Jadhav</t>
+  </si>
+  <si>
+    <t>Vinod Kale</t>
+  </si>
+  <si>
+    <t>Rajendra Verma</t>
+  </si>
+  <si>
+    <t>Raj Singh</t>
+  </si>
+  <si>
+    <t>Santosh Kale</t>
+  </si>
+  <si>
+    <t>Sameer Shinde</t>
+  </si>
+  <si>
+    <t>Vinod Singh</t>
+  </si>
+  <si>
+    <t>Kiran Katekar</t>
+  </si>
+  <si>
+    <t>Ashok Singhania</t>
+  </si>
+  <si>
+    <t>Viresh Pal</t>
+  </si>
+  <si>
+    <t>Vinod Kelkar</t>
+  </si>
+  <si>
+    <t>Zora Shaikh</t>
+  </si>
+  <si>
+    <t>Abdul Shaikh</t>
+  </si>
+  <si>
+    <t>Ravi Verman</t>
+  </si>
+  <si>
+    <t>Kiran Bhor</t>
+  </si>
+  <si>
+    <t>Unique</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>Emp. ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,16 +186,62 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -106,11 +249,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -119,6 +277,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -443,54 +614,330 @@
   <dimension ref="A1:E102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="5" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="21.140625" customWidth="1"/>
     <col min="8" max="8" width="32.5703125" customWidth="1"/>
     <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="26.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" ht="21.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="21.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" ht="21.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" ht="21.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" ht="21.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-    </row>
-    <row r="19" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
+    <row r="1" spans="1:5" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5">
+        <v>29</v>
+      </c>
+      <c r="D2" s="6" cm="1">
+        <f t="array" ref="D2:D8">_xlfn.UNIQUE(C2:C21)</f>
+        <v>29</v>
+      </c>
+      <c r="E2" s="6" cm="1">
+        <f t="array" ref="E2:E8">FREQUENCY(C2:C21,D2:D7)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5">
+        <v>20</v>
+      </c>
+      <c r="D3" s="6">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5">
+        <v>33</v>
+      </c>
+      <c r="D4" s="6">
+        <v>33</v>
+      </c>
+      <c r="E4" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="5">
+        <v>20</v>
+      </c>
+      <c r="D5" s="6">
+        <v>21</v>
+      </c>
+      <c r="E5" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="5">
+        <v>29</v>
+      </c>
+      <c r="D6" s="6">
+        <v>28</v>
+      </c>
+      <c r="E6" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5">
+        <v>33</v>
+      </c>
+      <c r="D7" s="6">
+        <v>27</v>
+      </c>
+      <c r="E7" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>21</v>
+      </c>
+      <c r="D8" s="6">
+        <v>23</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="5">
+        <v>29</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="5">
+        <v>29</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5">
+        <v>28</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5">
+        <v>20</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="5">
+        <v>27</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="5">
+        <v>21</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>28</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="5">
+        <v>27</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="5">
+        <v>20</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="5">
+        <v>5</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="5">
+        <v>29</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="5">
+        <v>10</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>28</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="5">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="5">
+        <v>27</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="5">
+        <v>23</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
     </row>
     <row r="23" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
@@ -1045,66 +1492,334 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB3672A7-A5F2-45D5-967E-9D3EF69C8DBD}">
-  <dimension ref="A1:G102"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{497855BE-96D4-4D74-85B0-4A1D3E1A851B}">
+  <dimension ref="A1:E102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="5" width="28.28515625" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="21.140625" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="21.140625" customWidth="1"/>
     <col min="8" max="8" width="32.5703125" customWidth="1"/>
     <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:7" ht="21.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:7" ht="21.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:7" ht="21.2" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:7" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-    </row>
-    <row r="19" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
+    <row r="1" spans="1:5" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5">
+        <v>29</v>
+      </c>
+      <c r="D2" s="6" cm="1">
+        <f t="array" ref="D2:D8">_xlfn.UNIQUE(C2:C21)</f>
+        <v>29</v>
+      </c>
+      <c r="E2" s="6" cm="1">
+        <f t="array" ref="E2:E8">FREQUENCY(C2:C21,D2:D7)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5">
+        <v>20</v>
+      </c>
+      <c r="D3" s="6">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5">
+        <v>33</v>
+      </c>
+      <c r="D4" s="6">
+        <v>33</v>
+      </c>
+      <c r="E4" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="5">
+        <v>20</v>
+      </c>
+      <c r="D5" s="6">
+        <v>21</v>
+      </c>
+      <c r="E5" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="5">
+        <v>29</v>
+      </c>
+      <c r="D6" s="6">
+        <v>28</v>
+      </c>
+      <c r="E6" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5">
+        <v>33</v>
+      </c>
+      <c r="D7" s="6">
+        <v>27</v>
+      </c>
+      <c r="E7" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>21</v>
+      </c>
+      <c r="D8" s="6">
+        <v>23</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="5">
+        <v>29</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="5">
+        <v>29</v>
+      </c>
+      <c r="D10" s="6"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" ht="20.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5">
+        <v>28</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5">
+        <v>20</v>
+      </c>
+      <c r="D12" s="6"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="5">
+        <v>27</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="5">
+        <v>21</v>
+      </c>
+      <c r="D14" s="6"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="5">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>28</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="5">
+        <v>27</v>
+      </c>
+      <c r="D16" s="6"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="5">
+        <v>20</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="5">
+        <v>5</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="5">
+        <v>29</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="5">
+        <v>10</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>28</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="5">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="5">
+        <v>27</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="5">
+        <v>23</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
     </row>
     <row r="23" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
@@ -1655,4 +2370,832 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB3672A7-A5F2-45D5-967E-9D3EF69C8DBD}">
+  <dimension ref="A1:G103"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="3" max="4" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" customWidth="1"/>
+    <col min="8" max="8" width="32.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9"/>
+      <c r="E1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2">
+        <f ca="1">LOOKUP(E2,B2:B21,C2:C3)</f>
+        <v>27</v>
+      </c>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="20.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>10</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>5</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>10</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="5">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+    </row>
+    <row r="27" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+    </row>
+    <row r="28" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+    </row>
+    <row r="29" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+    </row>
+    <row r="37" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+    </row>
+    <row r="48" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+    </row>
+    <row r="49" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+    </row>
+    <row r="54" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+    </row>
+    <row r="56" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+    </row>
+    <row r="57" spans="1:5" ht="21.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+    </row>
+    <row r="60" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+    </row>
+    <row r="61" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+    </row>
+    <row r="62" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="2"/>
+    </row>
+    <row r="87" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="2"/>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="2"/>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+    </row>
+    <row r="91" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+    </row>
+    <row r="93" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+    </row>
+    <row r="94" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="E95" s="2"/>
+    </row>
+    <row r="96" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+    </row>
+    <row r="97" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A97" s="1"/>
+      <c r="B97" s="1"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+    </row>
+    <row r="98" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="1"/>
+      <c r="B98" s="1"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+    </row>
+    <row r="99" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="1"/>
+      <c r="B99" s="1"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+    </row>
+    <row r="100" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A100" s="1"/>
+      <c r="B100" s="1"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+    </row>
+    <row r="101" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A101" s="1"/>
+      <c r="B101" s="1"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+    </row>
+    <row r="102" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A102" s="1"/>
+      <c r="B102" s="1"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+    </row>
+    <row r="103" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A103" s="1"/>
+      <c r="B103" s="1"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="E103" s="2"/>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E21" xr:uid="{A88F6C8E-9921-4600-9543-9290776E1EC4}">
+      <formula1>$E$2:$E$21</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2" xr:uid="{9C34C92A-DCAF-4CD7-BF58-3E534A0F4F74}">
+      <formula1>$B$2:$B$21</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>